--- a/output/pdf_financials_xlsx/DIV.xlsx
+++ b/output/pdf_financials_xlsx/DIV.xlsx
@@ -3058,19 +3058,19 @@
         <v>2.968</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.939</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.409</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.031</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>19.692</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.609</v>
       </c>
     </row>
     <row r="35">
@@ -3174,19 +3174,19 @@
         <v>2.968</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.939</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>7.409</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>4.031</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>19.692</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.609</v>
       </c>
     </row>
     <row r="37">
@@ -3870,19 +3870,19 @@
         <v>8.686999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>14.147</v>
+        <v>5.208</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.906000000000001</v>
+        <v>2.497</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.491</v>
+        <v>1.46</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>18.46</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/DIV.xlsx
+++ b/output/pdf_financials_xlsx/DIV.xlsx
@@ -39655,7 +39655,11 @@
           <t>Additions to intangible assets 9(h)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -41124,7 +41128,11 @@
           <t>Additions to intangible assets 9(g)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -42225,7 +42233,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -43427,7 +43439,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -44710,7 +44726,11 @@
           <t>Addition to intangible assets</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
